--- a/artfynd/A 13484-2022 artfynd.xlsx
+++ b/artfynd/A 13484-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13484-2022 artfynd.xlsx
+++ b/artfynd/A 13484-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102897624</v>
+        <v>104025304</v>
       </c>
       <c r="B2" t="n">
         <v>90653</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564769.5383342063</v>
+        <v>564769.5202202883</v>
       </c>
       <c r="R2" t="n">
-        <v>7014875.119072968</v>
+        <v>7014876.019737518</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,15 +775,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1019,7 +1023,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102897627</v>
+        <v>104025351</v>
       </c>
       <c r="B5" t="n">
         <v>77506</v>
@@ -1059,13 +1063,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564748.3946394868</v>
+        <v>564748.3765314217</v>
       </c>
       <c r="R5" t="n">
-        <v>7014917.041983755</v>
+        <v>7014917.942636584</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,22 +1093,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,25 +1122,29 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102897628</v>
+        <v>104025267</v>
       </c>
       <c r="B6" t="n">
         <v>76909</v>
@@ -1176,13 +1184,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564717.0925088424</v>
+        <v>564717.9943632418</v>
       </c>
       <c r="R6" t="n">
-        <v>7015015.523120199</v>
+        <v>7015015.541244478</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1206,22 +1214,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,15 +1244,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1369,7 +1381,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102897623</v>
+        <v>104025265</v>
       </c>
       <c r="B8" t="n">
         <v>77259</v>
@@ -1409,13 +1421,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564779.3815740277</v>
+        <v>564779.3634574157</v>
       </c>
       <c r="R8" t="n">
-        <v>7014834.319970946</v>
+        <v>7014835.22064689</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1439,22 +1451,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,15 +1481,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1593,7 +1609,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>102897630</v>
+        <v>104025294</v>
       </c>
       <c r="B10" t="n">
         <v>77595</v>
@@ -1629,17 +1645,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storberget, Jmt</t>
+          <t>Storberget-Storbergetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564809.9746247885</v>
+        <v>564810.8764535646</v>
       </c>
       <c r="R10" t="n">
-        <v>7015107.488796824</v>
+        <v>7015107.506947247</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1663,22 +1679,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,28 +1708,32 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>lodyta stor sten</t>
+          <t>Lodyta på större block</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104025351</v>
+        <v>104025296</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
+        <v>77177</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,21 +1746,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1750,10 +1770,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564748.3765314217</v>
+        <v>564770.8387406996</v>
       </c>
       <c r="R11" t="n">
-        <v>7014917.942636584</v>
+        <v>7014855.322528169</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1805,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1815,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,11 +1826,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1831,10 +1846,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104025294</v>
+        <v>104025261</v>
       </c>
       <c r="B12" t="n">
-        <v>77595</v>
+        <v>77258</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,38 +1858,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6450</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Storberget-Storbergetjärnen, Jmt</t>
+          <t>Storberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564810.8764535646</v>
+        <v>564756.9661518441</v>
       </c>
       <c r="R12" t="n">
-        <v>7015107.506947247</v>
+        <v>7014872.163161455</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1906,7 +1921,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1916,7 +1931,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,11 +1942,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Lodyta på större block</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1945,586 +1955,6 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>104025304</v>
-      </c>
-      <c r="B13" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Storberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>564769.5202202883</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7014876.019737518</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>104025296</v>
-      </c>
-      <c r="B14" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>353</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Cladonia parasitica</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Storberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>564770.8387406996</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7014855.322528169</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>104025265</v>
-      </c>
-      <c r="B15" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Storberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>564779.3634574157</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7014835.22064689</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>104025261</v>
-      </c>
-      <c r="B16" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Storberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>564756.9661518441</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7014872.163161455</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>104025267</v>
-      </c>
-      <c r="B17" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>6437</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Calicium denigratum</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Storberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>564717.9943632418</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7015015.541244478</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
